--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_h_6.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_h_6.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02252821164919743</v>
+        <v>0.01704989445177033</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008424069880698449</v>
+        <v>0.008419790512046258</v>
       </c>
       <c r="C2" t="n">
-        <v>38178486</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>38178486</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>26908527</v>
+        <v>4305976</v>
       </c>
       <c r="L2" t="n">
-        <v>14905346</v>
+        <v>2166166</v>
       </c>
       <c r="M2" t="n">
-        <v>3613002</v>
+        <v>477754</v>
       </c>
       <c r="N2" t="n">
-        <v>182747</v>
+        <v>17556</v>
       </c>
       <c r="O2" t="n">
-        <v>2175021</v>
+        <v>275088</v>
       </c>
       <c r="P2" t="n">
-        <v>889954</v>
+        <v>112996</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999895095825195</v>
+        <v>0.999994158744812</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8716942667961121</v>
+        <v>0.8185819387435913</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7504937648773193</v>
+        <v>0.6667713522911072</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6839295029640198</v>
+        <v>0.5768359303474426</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3441303968429565</v>
+        <v>0.1203908771276474</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7405788898468018</v>
+        <v>0.6301321983337402</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8122256398200989</v>
+        <v>0.7535880208015442</v>
       </c>
       <c r="X2" t="n">
-        <v>38178486</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>38178486</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>29140882</v>
+        <v>4830872</v>
       </c>
       <c r="AG2" t="n">
-        <v>17992178</v>
+        <v>2998822</v>
       </c>
       <c r="AH2" t="n">
-        <v>4814446</v>
+        <v>802107</v>
       </c>
       <c r="AI2" t="n">
-        <v>355185</v>
+        <v>59151</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2757566</v>
+        <v>459696</v>
       </c>
       <c r="AK2" t="n">
-        <v>1080499</v>
+        <v>180138</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9564012289047241</v>
+        <v>0.9562515616416931</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113964438438416</v>
+        <v>0.9114683270454407</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8578895330429077</v>
+        <v>0.8577601909637451</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.661842405796051</v>
+        <v>0.6615037322044373</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019240140914917</v>
+        <v>0.9018846154212952</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314445853233337</v>
+        <v>0.9314607977867126</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.005574440992571259</v>
+        <v>0.004107981906075768</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002018402068565029</v>
+        <v>0.002017893641709253</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>26908527</v>
+        <v>4305976</v>
       </c>
       <c r="E3" t="n">
-        <v>3421860</v>
+        <v>720024</v>
       </c>
       <c r="F3" t="n">
-        <v>83915</v>
+        <v>16772</v>
       </c>
       <c r="G3" t="n">
-        <v>12278</v>
+        <v>1819</v>
       </c>
       <c r="H3" t="n">
-        <v>4807</v>
+        <v>949</v>
       </c>
       <c r="I3" t="n">
-        <v>328</v>
+        <v>39</v>
       </c>
       <c r="J3" t="n">
-        <v>60576313</v>
+        <v>10069583</v>
       </c>
       <c r="K3" t="n">
-        <v>64362773</v>
+        <v>10416109</v>
       </c>
       <c r="L3" t="n">
-        <v>74026918</v>
+        <v>12038217</v>
       </c>
       <c r="M3" t="n">
-        <v>91469663</v>
+        <v>15129631</v>
       </c>
       <c r="N3" t="n">
-        <v>97869827</v>
+        <v>16198227</v>
       </c>
       <c r="O3" t="n">
-        <v>94934402</v>
+        <v>15744537</v>
       </c>
       <c r="P3" t="n">
-        <v>97389187</v>
+        <v>16185612</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8842260241508484</v>
+        <v>0.8534154891967773</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7538266777992249</v>
+        <v>0.6573681235313416</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6433604955673218</v>
+        <v>0.5104804039001465</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3402602970600128</v>
+        <v>0.1961476653814316</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7110469937324524</v>
+        <v>0.5393935441970825</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7670238614082336</v>
+        <v>0.5841397643089294</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>29140882</v>
+        <v>4830872</v>
       </c>
       <c r="Z3" t="n">
-        <v>1197602</v>
+        <v>199161</v>
       </c>
       <c r="AA3" t="n">
-        <v>51676</v>
+        <v>8614</v>
       </c>
       <c r="AB3" t="n">
-        <v>41119</v>
+        <v>6858</v>
       </c>
       <c r="AC3" t="n">
-        <v>270</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>60576714</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>66995046</v>
+        <v>11149408</v>
       </c>
       <c r="AG3" t="n">
-        <v>77233139</v>
+        <v>12829512</v>
       </c>
       <c r="AH3" t="n">
-        <v>92341853</v>
+        <v>15347098</v>
       </c>
       <c r="AI3" t="n">
-        <v>98036644</v>
+        <v>16296228</v>
       </c>
       <c r="AJ3" t="n">
-        <v>95396441</v>
+        <v>15855995</v>
       </c>
       <c r="AK3" t="n">
-        <v>97515405</v>
+        <v>16209305</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575821757316589</v>
+        <v>0.9574463367462158</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099408984184265</v>
+        <v>0.9100549221038818</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8572993874549866</v>
+        <v>0.8570517301559448</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6613260507583618</v>
+        <v>0.6608754992485046</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014897346496582</v>
+        <v>0.901373565196991</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312487244606018</v>
+        <v>0.9312344789505005</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.05729277802078948</v>
+        <v>0.0457491853680346</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03188605624102609</v>
+        <v>0.03187338455984583</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3734730</v>
+        <v>898077</v>
       </c>
       <c r="E4" t="n">
-        <v>14905346</v>
+        <v>2166166</v>
       </c>
       <c r="F4" t="n">
-        <v>989568</v>
+        <v>197573</v>
       </c>
       <c r="G4" t="n">
-        <v>49068</v>
+        <v>13951</v>
       </c>
       <c r="H4" t="n">
-        <v>85418</v>
+        <v>17687</v>
       </c>
       <c r="I4" t="n">
-        <v>8766</v>
+        <v>1755</v>
       </c>
       <c r="J4" t="n">
-        <v>401</v>
+        <v>37</v>
       </c>
       <c r="K4" t="n">
-        <v>3960698</v>
+        <v>954311</v>
       </c>
       <c r="L4" t="n">
-        <v>4955373</v>
+        <v>1082573</v>
       </c>
       <c r="M4" t="n">
-        <v>1669709</v>
+        <v>350478</v>
       </c>
       <c r="N4" t="n">
-        <v>348293</v>
+        <v>128269</v>
       </c>
       <c r="O4" t="n">
-        <v>761899</v>
+        <v>161468</v>
       </c>
       <c r="P4" t="n">
-        <v>205744</v>
+        <v>36948</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999947547912598</v>
+        <v>0.999997079372406</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8779154419898987</v>
+        <v>0.8356359004974365</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7521564960479736</v>
+        <v>0.6620363593101501</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6630249619483948</v>
+        <v>0.5416334271430969</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3421844244003296</v>
+        <v>0.1492038816213608</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7255126237869263</v>
+        <v>0.5812428593635559</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7889778614044189</v>
+        <v>0.6581319570541382</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1240358</v>
+        <v>206326</v>
       </c>
       <c r="Z4" t="n">
-        <v>17992178</v>
+        <v>2998822</v>
       </c>
       <c r="AA4" t="n">
-        <v>499863</v>
+        <v>83312</v>
       </c>
       <c r="AB4" t="n">
-        <v>33214</v>
+        <v>5534</v>
       </c>
       <c r="AC4" t="n">
-        <v>6888</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>408</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1328425</v>
+        <v>221012</v>
       </c>
       <c r="AG4" t="n">
-        <v>1749152</v>
+        <v>291278</v>
       </c>
       <c r="AH4" t="n">
-        <v>797519</v>
+        <v>133011</v>
       </c>
       <c r="AI4" t="n">
-        <v>181476</v>
+        <v>30268</v>
       </c>
       <c r="AJ4" t="n">
-        <v>299860</v>
+        <v>50010</v>
       </c>
       <c r="AK4" t="n">
-        <v>79526</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9569913744926453</v>
+        <v>0.9568485021591187</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106681346893311</v>
+        <v>0.9107611179351807</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8575943112373352</v>
+        <v>0.8574058413505554</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6615840792655945</v>
+        <v>0.6611894369125366</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017068147659302</v>
+        <v>0.9016289710998535</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313466548919678</v>
+        <v>0.9313476085662842</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>149993</v>
+        <v>39046</v>
       </c>
       <c r="E5" t="n">
-        <v>1304464</v>
+        <v>305066</v>
       </c>
       <c r="F5" t="n">
-        <v>3613002</v>
+        <v>477754</v>
       </c>
       <c r="G5" t="n">
-        <v>127660</v>
+        <v>39429</v>
       </c>
       <c r="H5" t="n">
-        <v>384419</v>
+        <v>66927</v>
       </c>
       <c r="I5" t="n">
-        <v>36255</v>
+        <v>7665</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3523202</v>
+        <v>739604</v>
       </c>
       <c r="L5" t="n">
-        <v>4867563</v>
+        <v>1129044</v>
       </c>
       <c r="M5" t="n">
-        <v>2002826</v>
+        <v>458137</v>
       </c>
       <c r="N5" t="n">
-        <v>354333</v>
+        <v>71948</v>
       </c>
       <c r="O5" t="n">
-        <v>883878</v>
+        <v>234907</v>
       </c>
       <c r="P5" t="n">
-        <v>270315</v>
+        <v>80444</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999959468841553</v>
+        <v>0.9999977350234985</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9242176413536072</v>
+        <v>0.8968131542205811</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9005324840545654</v>
+        <v>0.8652767539024353</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9628117084503174</v>
+        <v>0.950742244720459</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9928851723670959</v>
+        <v>0.9878035187721252</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9833347797393799</v>
+        <v>0.9758543372154236</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9951794147491455</v>
+        <v>0.9928489327430725</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>48591</v>
+        <v>8102</v>
       </c>
       <c r="Z5" t="n">
-        <v>513866</v>
+        <v>85827</v>
       </c>
       <c r="AA5" t="n">
-        <v>4814446</v>
+        <v>802107</v>
       </c>
       <c r="AB5" t="n">
-        <v>59922</v>
+        <v>9994</v>
       </c>
       <c r="AC5" t="n">
-        <v>175205</v>
+        <v>29228</v>
       </c>
       <c r="AD5" t="n">
-        <v>3798</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1290847</v>
+        <v>214708</v>
       </c>
       <c r="AG5" t="n">
-        <v>1780731</v>
+        <v>296388</v>
       </c>
       <c r="AH5" t="n">
-        <v>801382</v>
+        <v>133784</v>
       </c>
       <c r="AI5" t="n">
-        <v>181895</v>
+        <v>30353</v>
       </c>
       <c r="AJ5" t="n">
-        <v>301333</v>
+        <v>50299</v>
       </c>
       <c r="AK5" t="n">
-        <v>79770</v>
+        <v>13302</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734771251678467</v>
+        <v>0.9734575748443604</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.964256227016449</v>
+        <v>0.9642016291618347</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838094711303711</v>
+        <v>0.9837478399276733</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963204860687256</v>
+        <v>0.9963071942329407</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939122796058655</v>
+        <v>0.9938895702362061</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983869791030884</v>
+        <v>0.9983822703361511</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>71115</v>
+        <v>15797</v>
       </c>
       <c r="E6" t="n">
-        <v>100815</v>
+        <v>20687</v>
       </c>
       <c r="F6" t="n">
-        <v>116178</v>
+        <v>25313</v>
       </c>
       <c r="G6" t="n">
-        <v>182747</v>
+        <v>17556</v>
       </c>
       <c r="H6" t="n">
-        <v>59178</v>
+        <v>9018</v>
       </c>
       <c r="I6" t="n">
-        <v>6977</v>
+        <v>1124</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>39140</v>
+        <v>6528</v>
       </c>
       <c r="Z6" t="n">
-        <v>32331</v>
+        <v>5399</v>
       </c>
       <c r="AA6" t="n">
-        <v>65578</v>
+        <v>10952</v>
       </c>
       <c r="AB6" t="n">
-        <v>355185</v>
+        <v>59151</v>
       </c>
       <c r="AC6" t="n">
-        <v>41960</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>2886</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>123</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>4685</v>
+        <v>1359</v>
       </c>
       <c r="E7" t="n">
-        <v>120097</v>
+        <v>34502</v>
       </c>
       <c r="F7" t="n">
-        <v>457767</v>
+        <v>104712</v>
       </c>
       <c r="G7" t="n">
-        <v>147788</v>
+        <v>67960</v>
       </c>
       <c r="H7" t="n">
-        <v>2175021</v>
+        <v>275088</v>
       </c>
       <c r="I7" t="n">
-        <v>153418</v>
+        <v>26365</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>168</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4867</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>178417</v>
+        <v>29802</v>
       </c>
       <c r="AB7" t="n">
-        <v>45627</v>
+        <v>7616</v>
       </c>
       <c r="AC7" t="n">
-        <v>2757566</v>
+        <v>459696</v>
       </c>
       <c r="AD7" t="n">
-        <v>72254</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>146</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>175</v>
+        <v>32</v>
       </c>
       <c r="E8" t="n">
-        <v>8137</v>
+        <v>2294</v>
       </c>
       <c r="F8" t="n">
-        <v>22281</v>
+        <v>6108</v>
       </c>
       <c r="G8" t="n">
-        <v>11499</v>
+        <v>5110</v>
       </c>
       <c r="H8" t="n">
-        <v>228077</v>
+        <v>66887</v>
       </c>
       <c r="I8" t="n">
-        <v>889954</v>
+        <v>112996</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>168</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>486</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1985</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1594</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>75537</v>
+        <v>12596</v>
       </c>
       <c r="AD8" t="n">
-        <v>1080499</v>
+        <v>180138</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
